--- a/ig/tru-exemples/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
+++ b/ig/tru-exemples/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-06T14:26:02+00:00</t>
+    <t>2024-03-11T15:09:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/tru-exemples/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
+++ b/ig/tru-exemples/ValueSet-fr-core-vs-encounter-identifier-type.xlsx
@@ -7,13 +7,13 @@
   </bookViews>
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
-    <sheet name="Include from fr-coreidentifie" r:id="rId4" sheetId="2"/>
+    <sheet name="Include from FR Core CodeSyst" r:id="rId4" sheetId="2"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="33">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-11T15:09:21+00:00</t>
+    <t>2024-03-11T15:35:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -99,19 +99,10 @@
     <t>BooleanType[true]</t>
   </si>
   <si>
-    <t>Concept</t>
-  </si>
-  <si>
-    <t>VN</t>
-  </si>
-  <si>
-    <t>Visit Number</t>
-  </si>
-  <si>
-    <t>MN</t>
-  </si>
-  <si>
-    <t>Movement Number</t>
+    <t>Codes</t>
+  </si>
+  <si>
+    <t>All codes</t>
   </si>
   <si>
     <t/>
@@ -120,7 +111,7 @@
     <t>System URI</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/CodeSystem/fr-coreidentifier-type</t>
+    <t>https://hl7.fr/ig/fhir/core/CodeSystem/fr-core-cs-identifier-type</t>
   </si>
 </sst>
 </file>
@@ -392,7 +383,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -403,40 +394,26 @@
       <c r="A1" t="s" s="1">
         <v>28</v>
       </c>
-      <c r="B1" t="s" s="1">
-        <v>22</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
         <v>29</v>
       </c>
-      <c r="B2" t="s" s="2">
-        <v>30</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="B5" t="s" s="2">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
